--- a/URUVS/Datasheets/URUV/02.2024/February_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/02.2024/February_RecordingData.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sophi\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\02.2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\02.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99E8ACF-5013-4961-A863-39ACEEFBD18E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E855F0EC-37E3-4EE9-AD39-10173B66D906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recordings" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,6 +24,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="190">
   <si>
     <t>DATE</t>
   </si>
@@ -580,6 +586,27 @@
   </si>
   <si>
     <t>FEBRUARY</t>
+  </si>
+  <si>
+    <t>MAXN_MUDCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STMUDCRAB</t>
+  </si>
+  <si>
+    <t>T1_FISHMUDCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STSWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>T1_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_ULAR</t>
   </si>
 </sst>
 </file>
@@ -783,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -793,9 +820,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -808,8 +835,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -821,9 +848,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="21" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -831,10 +858,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2206,16 +2230,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF2D75B-3330-44BB-BF8B-27BF0F133624}">
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="22" width="8.7265625" customWidth="1"/>
     <col min="23" max="26" width="8.7265625" style="4" customWidth="1"/>
     <col min="27" max="34" width="8.7265625" customWidth="1"/>
-    <col min="71" max="71" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>181</v>
       </c>
@@ -2426,11 +2450,38 @@
       <c r="BR1" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="BS1" s="40" t="s">
+      <c r="BS1" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT1" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="BU1" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="BV1" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW1" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="BX1" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="BY1" s="31" t="s">
+        <v>189</v>
+      </c>
+      <c r="BZ1" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="CA1" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="CB1" s="40" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>182</v>
       </c>
@@ -2446,7 +2497,7 @@
       <c r="E2" s="9">
         <v>4</v>
       </c>
-      <c r="F2" s="49" t="str">
+      <c r="F2" s="9" t="str">
         <f t="shared" ref="F2:F21" si="0">D2&amp;""&amp;E2</f>
         <v>D4</v>
       </c>
@@ -2646,9 +2697,27 @@
         <f>IF(BP2=0,"NA",BQ2-$AA2)</f>
         <v>NA</v>
       </c>
-      <c r="BS2" s="41"/>
+      <c r="BS2" s="36"/>
+      <c r="BT2" s="37"/>
+      <c r="BU2" s="38" t="str">
+        <f>IF(BS2=0,"NA",BT2-$AA2)</f>
+        <v>NA</v>
+      </c>
+      <c r="BV2" s="36"/>
+      <c r="BW2" s="37"/>
+      <c r="BX2" s="38" t="str">
+        <f>IF(BV2=0,"NA",BW2-$AA2)</f>
+        <v>NA</v>
+      </c>
+      <c r="BY2" s="36"/>
+      <c r="BZ2" s="37"/>
+      <c r="CA2" s="38" t="str">
+        <f>IF(BY2=0,"NA",BZ2-$AA2)</f>
+        <v>NA</v>
+      </c>
+      <c r="CB2" s="41"/>
     </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>182</v>
       </c>
@@ -2664,7 +2733,7 @@
       <c r="E3" s="9">
         <v>6</v>
       </c>
-      <c r="F3" s="49" t="str">
+      <c r="F3" s="9" t="str">
         <f t="shared" si="0"/>
         <v>L6</v>
       </c>
@@ -2866,9 +2935,35 @@
         <f t="shared" ref="BR3:BR20" si="14">IF(BP3=0,"NA",BQ3-$AA3)</f>
         <v>5.1504629629629643E-3</v>
       </c>
-      <c r="BS3" s="41"/>
+      <c r="BS3" s="36">
+        <v>1</v>
+      </c>
+      <c r="BT3" s="39">
+        <v>3.9108796296296294E-2</v>
+      </c>
+      <c r="BU3" s="38">
+        <f t="shared" ref="BU3:BU20" si="15">IF(BS3=0,"NA",BT3-$AA3)</f>
+        <v>3.1678240740740743E-2</v>
+      </c>
+      <c r="BV3" s="36">
+        <v>1</v>
+      </c>
+      <c r="BW3" s="39">
+        <v>2.4328703703703703E-2</v>
+      </c>
+      <c r="BX3" s="38">
+        <f t="shared" ref="BX3:BX20" si="16">IF(BV3=0,"NA",BW3-$AA3)</f>
+        <v>1.6898148148148148E-2</v>
+      </c>
+      <c r="BY3" s="36"/>
+      <c r="BZ3" s="39"/>
+      <c r="CA3" s="38" t="str">
+        <f t="shared" ref="CA3:CA20" si="17">IF(BY3=0,"NA",BZ3-$AA3)</f>
+        <v>NA</v>
+      </c>
+      <c r="CB3" s="41"/>
     </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>182</v>
       </c>
@@ -2884,7 +2979,7 @@
       <c r="E4" s="9">
         <v>5</v>
       </c>
-      <c r="F4" s="49" t="str">
+      <c r="F4" s="9" t="str">
         <f t="shared" si="0"/>
         <v>E5</v>
       </c>
@@ -3094,9 +3189,27 @@
         <f t="shared" si="14"/>
         <v>NA</v>
       </c>
-      <c r="BS4" s="41"/>
+      <c r="BS4" s="36"/>
+      <c r="BT4" s="37"/>
+      <c r="BU4" s="38" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="BV4" s="36"/>
+      <c r="BW4" s="37"/>
+      <c r="BX4" s="38" t="str">
+        <f t="shared" si="16"/>
+        <v>NA</v>
+      </c>
+      <c r="BY4" s="36"/>
+      <c r="BZ4" s="37"/>
+      <c r="CA4" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB4" s="41"/>
     </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>182</v>
       </c>
@@ -3112,7 +3225,7 @@
       <c r="E5" s="9">
         <v>4</v>
       </c>
-      <c r="F5" s="49" t="str">
+      <c r="F5" s="9" t="str">
         <f t="shared" si="0"/>
         <v>E4</v>
       </c>
@@ -3314,9 +3427,31 @@
         <f t="shared" si="14"/>
         <v>2.3611111111111116E-3</v>
       </c>
-      <c r="BS5" s="41"/>
+      <c r="BS5" s="36">
+        <v>1</v>
+      </c>
+      <c r="BT5" s="39">
+        <v>1.0717592592592593E-2</v>
+      </c>
+      <c r="BU5" s="38">
+        <f t="shared" si="15"/>
+        <v>6.5509259259259262E-3</v>
+      </c>
+      <c r="BV5" s="36"/>
+      <c r="BW5" s="39"/>
+      <c r="BX5" s="38" t="str">
+        <f t="shared" si="16"/>
+        <v>NA</v>
+      </c>
+      <c r="BY5" s="36"/>
+      <c r="BZ5" s="39"/>
+      <c r="CA5" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB5" s="41"/>
     </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>182</v>
       </c>
@@ -3332,7 +3467,7 @@
       <c r="E6" s="9">
         <v>5</v>
       </c>
-      <c r="F6" s="49" t="str">
+      <c r="F6" s="9" t="str">
         <f t="shared" si="0"/>
         <v>L5</v>
       </c>
@@ -3530,15 +3665,41 @@
         <v>2</v>
       </c>
       <c r="BQ6" s="39">
-        <v>2.0891203703703703E-2</v>
+        <v>8.6574074074074071E-3</v>
       </c>
       <c r="BR6" s="38">
         <f>IF(BP6=0,"NA",BQ6-$AA6)</f>
-        <v>1.255787037037037E-2</v>
-      </c>
-      <c r="BS6" s="41"/>
+        <v>3.2407407407407385E-4</v>
+      </c>
+      <c r="BS6" s="36">
+        <v>1</v>
+      </c>
+      <c r="BT6" s="39">
+        <v>4.3518518518518519E-2</v>
+      </c>
+      <c r="BU6" s="38">
+        <f>IF(BS6=0,"NA",BT6-$AA6)</f>
+        <v>3.5185185185185187E-2</v>
+      </c>
+      <c r="BV6" s="36">
+        <v>1</v>
+      </c>
+      <c r="BW6" s="39">
+        <v>1.4421296296296297E-2</v>
+      </c>
+      <c r="BX6" s="38">
+        <f>IF(BV6=0,"NA",BW6-$AA6)</f>
+        <v>6.0879629629629634E-3</v>
+      </c>
+      <c r="BY6" s="36"/>
+      <c r="BZ6" s="39"/>
+      <c r="CA6" s="38" t="str">
+        <f>IF(BY6=0,"NA",BZ6-$AA6)</f>
+        <v>NA</v>
+      </c>
+      <c r="CB6" s="41"/>
     </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>182</v>
       </c>
@@ -3554,7 +3715,7 @@
       <c r="E7" s="9">
         <v>5</v>
       </c>
-      <c r="F7" s="49" t="str">
+      <c r="F7" s="9" t="str">
         <f t="shared" si="0"/>
         <v>D5</v>
       </c>
@@ -3745,7 +3906,7 @@
         <v>12</v>
       </c>
       <c r="BO7" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="BO7:BO24" si="18">IF(BM7=0,"NA",BN7-$AA7)</f>
         <v>NA</v>
       </c>
       <c r="BP7" s="36">
@@ -3755,12 +3916,34 @@
         <v>1.1666666666666667E-2</v>
       </c>
       <c r="BR7" s="38">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="BR7:BR24" si="19">IF(BP7=0,"NA",BQ7-$AA7)</f>
         <v>4.7222222222222231E-3</v>
       </c>
-      <c r="BS7" s="41"/>
+      <c r="BS7" s="36">
+        <v>1</v>
+      </c>
+      <c r="BT7" s="39">
+        <v>1.1666666666666667E-2</v>
+      </c>
+      <c r="BU7" s="38">
+        <f t="shared" si="15"/>
+        <v>4.7222222222222231E-3</v>
+      </c>
+      <c r="BV7" s="36"/>
+      <c r="BW7" s="39"/>
+      <c r="BX7" s="38" t="str">
+        <f t="shared" ref="BX7:BX24" si="20">IF(BV7=0,"NA",BW7-$AA7)</f>
+        <v>NA</v>
+      </c>
+      <c r="BY7" s="36"/>
+      <c r="BZ7" s="39"/>
+      <c r="CA7" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB7" s="41"/>
     </row>
-    <row r="8" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>182</v>
       </c>
@@ -3776,7 +3959,7 @@
       <c r="E8" s="9">
         <v>4</v>
       </c>
-      <c r="F8" s="49" t="str">
+      <c r="F8" s="9" t="str">
         <f t="shared" si="0"/>
         <v>L4</v>
       </c>
@@ -3969,7 +4152,7 @@
         <v>12</v>
       </c>
       <c r="BO8" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP8" s="36">
@@ -3979,12 +4162,38 @@
         <v>7.0486111111111105E-3</v>
       </c>
       <c r="BR8" s="38">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>3.5763888888888885E-3</v>
       </c>
-      <c r="BS8" s="41"/>
+      <c r="BS8" s="36">
+        <v>1</v>
+      </c>
+      <c r="BT8" s="39">
+        <v>5.0115740740740737E-3</v>
+      </c>
+      <c r="BU8" s="38">
+        <f t="shared" si="15"/>
+        <v>1.5393518518518516E-3</v>
+      </c>
+      <c r="BV8" s="36">
+        <v>1</v>
+      </c>
+      <c r="BW8" s="39">
+        <v>7.6273148148148151E-3</v>
+      </c>
+      <c r="BX8" s="38">
+        <f t="shared" si="20"/>
+        <v>4.155092592592593E-3</v>
+      </c>
+      <c r="BY8" s="36"/>
+      <c r="BZ8" s="39"/>
+      <c r="CA8" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB8" s="41"/>
     </row>
-    <row r="9" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>182</v>
       </c>
@@ -4000,7 +4209,7 @@
       <c r="E9" s="9">
         <v>6</v>
       </c>
-      <c r="F9" s="49" t="str">
+      <c r="F9" s="9" t="str">
         <f t="shared" si="0"/>
         <v>D6</v>
       </c>
@@ -4193,7 +4402,7 @@
         <v>12</v>
       </c>
       <c r="BO9" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP9" s="36">
@@ -4203,12 +4412,30 @@
         <v>12</v>
       </c>
       <c r="BR9" s="38" t="str">
-        <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="BS9" s="41"/>
+        <f t="shared" si="19"/>
+        <v>NA</v>
+      </c>
+      <c r="BS9" s="36"/>
+      <c r="BT9" s="37"/>
+      <c r="BU9" s="38" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="BV9" s="36"/>
+      <c r="BW9" s="37"/>
+      <c r="BX9" s="38" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY9" s="36"/>
+      <c r="BZ9" s="37"/>
+      <c r="CA9" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB9" s="41"/>
     </row>
-    <row r="10" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>182</v>
       </c>
@@ -4224,7 +4451,7 @@
       <c r="E10" s="9">
         <v>6</v>
       </c>
-      <c r="F10" s="49" t="str">
+      <c r="F10" s="9" t="str">
         <f t="shared" si="0"/>
         <v>E6</v>
       </c>
@@ -4303,10 +4530,10 @@
         <v>114</v>
       </c>
       <c r="AG10" s="34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH10" s="35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI10" s="36">
         <v>1</v>
@@ -4415,7 +4642,7 @@
         <v>12</v>
       </c>
       <c r="BO10" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP10" s="36">
@@ -4425,12 +4652,30 @@
         <v>2.8194444444444442E-2</v>
       </c>
       <c r="BR10" s="38">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>2.1249999999999998E-2</v>
       </c>
-      <c r="BS10" s="41"/>
+      <c r="BS10" s="36"/>
+      <c r="BT10" s="37"/>
+      <c r="BU10" s="38" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="BV10" s="36"/>
+      <c r="BW10" s="39"/>
+      <c r="BX10" s="38" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY10" s="36"/>
+      <c r="BZ10" s="39"/>
+      <c r="CA10" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB10" s="41"/>
     </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>182</v>
       </c>
@@ -4446,7 +4691,7 @@
       <c r="E11" s="9">
         <v>1</v>
       </c>
-      <c r="F11" s="49" t="str">
+      <c r="F11" s="9" t="str">
         <f t="shared" si="0"/>
         <v>E1</v>
       </c>
@@ -4637,7 +4882,7 @@
         <v>12</v>
       </c>
       <c r="BO11" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP11" s="36">
@@ -4647,12 +4892,34 @@
         <v>2.6111111111111113E-2</v>
       </c>
       <c r="BR11" s="38">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>2.2141203703703705E-2</v>
       </c>
-      <c r="BS11" s="41"/>
+      <c r="BS11" s="36"/>
+      <c r="BT11" s="37"/>
+      <c r="BU11" s="38" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="BV11" s="36"/>
+      <c r="BW11" s="39"/>
+      <c r="BX11" s="38" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY11" s="36">
+        <v>1</v>
+      </c>
+      <c r="BZ11" s="39">
+        <v>3.0763888888888889E-2</v>
+      </c>
+      <c r="CA11" s="38">
+        <f t="shared" si="17"/>
+        <v>2.6793981481481481E-2</v>
+      </c>
+      <c r="CB11" s="41"/>
     </row>
-    <row r="12" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>182</v>
       </c>
@@ -4668,7 +4935,7 @@
       <c r="E12" s="9">
         <v>2</v>
       </c>
-      <c r="F12" s="49" t="str">
+      <c r="F12" s="9" t="str">
         <f t="shared" si="0"/>
         <v>E2</v>
       </c>
@@ -4859,7 +5126,7 @@
         <v>12</v>
       </c>
       <c r="BO12" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP12" s="36">
@@ -4869,12 +5136,30 @@
         <v>1.3923611111111111E-2</v>
       </c>
       <c r="BR12" s="38">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>6.9791666666666665E-3</v>
       </c>
-      <c r="BS12" s="41"/>
+      <c r="BS12" s="36"/>
+      <c r="BT12" s="37"/>
+      <c r="BU12" s="38" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="BV12" s="36"/>
+      <c r="BW12" s="39"/>
+      <c r="BX12" s="38" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY12" s="36"/>
+      <c r="BZ12" s="39"/>
+      <c r="CA12" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB12" s="41"/>
     </row>
-    <row r="13" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>182</v>
       </c>
@@ -4890,7 +5175,7 @@
       <c r="E13" s="9">
         <v>3</v>
       </c>
-      <c r="F13" s="49" t="str">
+      <c r="F13" s="9" t="str">
         <f t="shared" si="0"/>
         <v>E3</v>
       </c>
@@ -5083,7 +5368,7 @@
         <v>12</v>
       </c>
       <c r="BO13" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP13" s="36">
@@ -5093,12 +5378,30 @@
         <v>4.5601851851851853E-3</v>
       </c>
       <c r="BR13" s="38">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>3.9351851851851874E-4</v>
       </c>
-      <c r="BS13" s="41"/>
+      <c r="BS13" s="36"/>
+      <c r="BT13" s="37"/>
+      <c r="BU13" s="38" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="BV13" s="36"/>
+      <c r="BW13" s="39"/>
+      <c r="BX13" s="38" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY13" s="36"/>
+      <c r="BZ13" s="39"/>
+      <c r="CA13" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB13" s="41"/>
     </row>
-    <row r="14" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>182</v>
       </c>
@@ -5114,7 +5417,7 @@
       <c r="E14" s="9">
         <v>2</v>
       </c>
-      <c r="F14" s="49" t="str">
+      <c r="F14" s="9" t="str">
         <f t="shared" si="0"/>
         <v>D2</v>
       </c>
@@ -5305,7 +5608,7 @@
         <v>12</v>
       </c>
       <c r="BO14" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP14" s="36">
@@ -5315,12 +5618,34 @@
         <v>12</v>
       </c>
       <c r="BR14" s="38" t="str">
-        <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="BS14" s="41"/>
+        <f t="shared" si="19"/>
+        <v>NA</v>
+      </c>
+      <c r="BS14" s="36"/>
+      <c r="BT14" s="37"/>
+      <c r="BU14" s="38" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="BV14" s="36">
+        <v>2</v>
+      </c>
+      <c r="BW14" s="39">
+        <v>9.5486111111111119E-3</v>
+      </c>
+      <c r="BX14" s="38">
+        <f t="shared" si="20"/>
+        <v>2.6041666666666678E-3</v>
+      </c>
+      <c r="BY14" s="36"/>
+      <c r="BZ14" s="37"/>
+      <c r="CA14" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB14" s="41"/>
     </row>
-    <row r="15" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>182</v>
       </c>
@@ -5336,7 +5661,7 @@
       <c r="E15" s="9">
         <v>3</v>
       </c>
-      <c r="F15" s="49" t="str">
+      <c r="F15" s="9" t="str">
         <f t="shared" si="0"/>
         <v>D3</v>
       </c>
@@ -5527,7 +5852,7 @@
         <v>12</v>
       </c>
       <c r="BO15" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP15" s="36">
@@ -5537,12 +5862,30 @@
         <v>12</v>
       </c>
       <c r="BR15" s="38" t="str">
-        <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="BS15" s="41"/>
+        <f t="shared" si="19"/>
+        <v>NA</v>
+      </c>
+      <c r="BS15" s="36"/>
+      <c r="BT15" s="37"/>
+      <c r="BU15" s="38" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="BV15" s="36"/>
+      <c r="BW15" s="37"/>
+      <c r="BX15" s="38" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY15" s="36"/>
+      <c r="BZ15" s="37"/>
+      <c r="CA15" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB15" s="41"/>
     </row>
-    <row r="16" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>182</v>
       </c>
@@ -5558,7 +5901,7 @@
       <c r="E16" s="9">
         <v>1</v>
       </c>
-      <c r="F16" s="49" t="str">
+      <c r="F16" s="9" t="str">
         <f t="shared" si="0"/>
         <v>D1</v>
       </c>
@@ -5755,7 +6098,7 @@
         <v>12</v>
       </c>
       <c r="BO16" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP16" s="36" t="s">
@@ -5765,12 +6108,30 @@
         <v>12</v>
       </c>
       <c r="BR16" s="38" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="BS16" s="41"/>
+      <c r="BS16" s="36"/>
+      <c r="BT16" s="37"/>
+      <c r="BU16" s="38" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="BV16" s="36"/>
+      <c r="BW16" s="39"/>
+      <c r="BX16" s="38" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY16" s="36"/>
+      <c r="BZ16" s="39"/>
+      <c r="CA16" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB16" s="41"/>
     </row>
-    <row r="17" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>182</v>
       </c>
@@ -5786,7 +6147,7 @@
       <c r="E17" s="9">
         <v>1</v>
       </c>
-      <c r="F17" s="49" t="str">
+      <c r="F17" s="9" t="str">
         <f t="shared" si="0"/>
         <v>D1</v>
       </c>
@@ -5940,7 +6301,7 @@
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="BD17" s="47">
+      <c r="BD17" s="36">
         <v>1</v>
       </c>
       <c r="BE17" s="39">
@@ -5950,7 +6311,7 @@
         <f t="shared" si="10"/>
         <v>3.740740740740741E-2</v>
       </c>
-      <c r="BG17" s="47">
+      <c r="BG17" s="36">
         <v>0</v>
       </c>
       <c r="BH17" s="39" t="s">
@@ -5960,7 +6321,7 @@
         <f t="shared" si="11"/>
         <v>NA</v>
       </c>
-      <c r="BJ17" s="47">
+      <c r="BJ17" s="36">
         <v>10</v>
       </c>
       <c r="BK17" s="39">
@@ -5977,7 +6338,7 @@
         <v>12</v>
       </c>
       <c r="BO17" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP17" s="36">
@@ -5987,12 +6348,34 @@
         <v>3.7500000000000003E-3</v>
       </c>
       <c r="BR17" s="38">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>2.7777777777777827E-4</v>
       </c>
-      <c r="BS17" s="41"/>
+      <c r="BS17" s="36">
+        <v>2</v>
+      </c>
+      <c r="BT17" s="39">
+        <v>1.7372685185185185E-2</v>
+      </c>
+      <c r="BU17" s="38">
+        <f t="shared" si="15"/>
+        <v>1.3900462962962963E-2</v>
+      </c>
+      <c r="BV17" s="36"/>
+      <c r="BW17" s="39"/>
+      <c r="BX17" s="38" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY17" s="36"/>
+      <c r="BZ17" s="39"/>
+      <c r="CA17" s="38" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB17" s="41"/>
     </row>
-    <row r="18" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>182</v>
       </c>
@@ -6008,7 +6391,7 @@
       <c r="E18" s="9">
         <v>3</v>
       </c>
-      <c r="F18" s="49" t="str">
+      <c r="F18" s="9" t="str">
         <f t="shared" si="0"/>
         <v>L3</v>
       </c>
@@ -6199,7 +6582,7 @@
         <v>12</v>
       </c>
       <c r="BO18" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP18" s="36">
@@ -6209,12 +6592,34 @@
         <v>1.4884259259259259E-2</v>
       </c>
       <c r="BR18" s="38">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>1.1412037037037037E-2</v>
       </c>
-      <c r="BS18" s="41"/>
+      <c r="BS18" s="36"/>
+      <c r="BT18" s="37"/>
+      <c r="BU18" s="38" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="BV18" s="36"/>
+      <c r="BW18" s="39"/>
+      <c r="BX18" s="38" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY18" s="36">
+        <v>1</v>
+      </c>
+      <c r="BZ18" s="39">
+        <v>3.9351851851851853E-2</v>
+      </c>
+      <c r="CA18" s="38">
+        <f t="shared" si="17"/>
+        <v>3.5879629629629629E-2</v>
+      </c>
+      <c r="CB18" s="41"/>
     </row>
-    <row r="19" spans="1:71" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:80" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>182</v>
       </c>
@@ -6230,7 +6635,7 @@
       <c r="E19" s="9">
         <v>2</v>
       </c>
-      <c r="F19" s="49" t="str">
+      <c r="F19" s="9" t="str">
         <f t="shared" si="0"/>
         <v>L2</v>
       </c>
@@ -6421,7 +6826,7 @@
         <v>12</v>
       </c>
       <c r="BO19" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="BP19" s="36">
@@ -6431,12 +6836,38 @@
         <v>4.6064814814814814E-3</v>
       </c>
       <c r="BR19" s="38">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>1.9675925925925937E-4</v>
       </c>
-      <c r="BS19" s="41"/>
+      <c r="BS19" s="36">
+        <v>1</v>
+      </c>
+      <c r="BT19" s="39">
+        <v>4.6689814814814816E-2</v>
+      </c>
+      <c r="BU19" s="38">
+        <f t="shared" si="15"/>
+        <v>4.2280092592592591E-2</v>
+      </c>
+      <c r="BV19" s="36"/>
+      <c r="BW19" s="39"/>
+      <c r="BX19" s="38" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY19" s="36">
+        <v>1</v>
+      </c>
+      <c r="BZ19" s="39">
+        <v>1.4791666666666667E-2</v>
+      </c>
+      <c r="CA19" s="38">
+        <f t="shared" si="17"/>
+        <v>1.0381944444444444E-2</v>
+      </c>
+      <c r="CB19" s="41"/>
     </row>
-    <row r="20" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:80" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
         <v>182</v>
       </c>
@@ -6542,7 +6973,7 @@
       <c r="AJ20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AK20" s="48" t="str">
+      <c r="AK20" s="47" t="str">
         <f t="shared" si="3"/>
         <v>NA</v>
       </c>
@@ -6552,7 +6983,7 @@
       <c r="AM20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AN20" s="48" t="str">
+      <c r="AN20" s="47" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
@@ -6562,7 +6993,7 @@
       <c r="AP20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AQ20" s="48" t="str">
+      <c r="AQ20" s="47" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
@@ -6572,7 +7003,7 @@
       <c r="AS20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AT20" s="48" t="str">
+      <c r="AT20" s="47" t="str">
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
@@ -6582,7 +7013,7 @@
       <c r="AV20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AW20" s="48" t="str">
+      <c r="AW20" s="47" t="str">
         <f t="shared" si="7"/>
         <v>NA</v>
       </c>
@@ -6592,7 +7023,7 @@
       <c r="AY20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AZ20" s="48" t="str">
+      <c r="AZ20" s="47" t="str">
         <f t="shared" si="8"/>
         <v>NA</v>
       </c>
@@ -6602,7 +7033,7 @@
       <c r="BB20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="BC20" s="48" t="str">
+      <c r="BC20" s="47" t="str">
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
@@ -6612,7 +7043,7 @@
       <c r="BE20" s="46">
         <v>4.0162037037037033E-3</v>
       </c>
-      <c r="BF20" s="48">
+      <c r="BF20" s="47">
         <f t="shared" si="10"/>
         <v>1.9675925925925894E-4</v>
       </c>
@@ -6622,7 +7053,7 @@
       <c r="BH20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="BI20" s="48" t="str">
+      <c r="BI20" s="47" t="str">
         <f t="shared" si="11"/>
         <v>NA</v>
       </c>
@@ -6632,7 +7063,7 @@
       <c r="BK20" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="BL20" s="48" t="str">
+      <c r="BL20" s="47" t="str">
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
@@ -6642,8 +7073,8 @@
       <c r="BN20" s="46">
         <v>7.7314814814814815E-3</v>
       </c>
-      <c r="BO20" s="48">
-        <f t="shared" si="13"/>
+      <c r="BO20" s="47">
+        <f t="shared" si="18"/>
         <v>3.9120370370370368E-3</v>
       </c>
       <c r="BP20" s="44">
@@ -6652,14 +7083,36 @@
       <c r="BQ20" s="46">
         <v>1.0520833333333333E-2</v>
       </c>
-      <c r="BR20" s="48">
-        <f t="shared" si="14"/>
+      <c r="BR20" s="47">
+        <f t="shared" si="19"/>
         <v>6.7013888888888887E-3</v>
       </c>
-      <c r="BS20" s="45"/>
+      <c r="BS20" s="44">
+        <v>1</v>
+      </c>
+      <c r="BT20" s="46">
+        <v>2.1678240740740741E-2</v>
+      </c>
+      <c r="BU20" s="47">
+        <f t="shared" si="15"/>
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="BV20" s="44"/>
+      <c r="BW20" s="46"/>
+      <c r="BX20" s="47" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="BY20" s="44"/>
+      <c r="BZ20" s="46"/>
+      <c r="CA20" s="47" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CB20" s="45"/>
     </row>
-    <row r="21" spans="1:71" x14ac:dyDescent="0.35">
-      <c r="F21" s="50" t="str">
+    <row r="21" spans="1:80" x14ac:dyDescent="0.35">
+      <c r="F21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>

--- a/URUVS/Datasheets/URUV/02.2024/February_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/02.2024/February_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\02.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E855F0EC-37E3-4EE9-AD39-10173B66D906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18884B9E-0A58-476E-A66A-0135EB3E539B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recordings" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="192">
   <si>
     <t>DATE</t>
   </si>
@@ -607,6 +607,12 @@
   </si>
   <si>
     <t>MAXN_ULAR</t>
+  </si>
+  <si>
+    <t>TIME_1STULAR</t>
+  </si>
+  <si>
+    <t>T1_ULAR</t>
   </si>
 </sst>
 </file>
@@ -2472,10 +2478,10 @@
         <v>189</v>
       </c>
       <c r="BZ1" s="32" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="CA1" s="33" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="CB1" s="40" t="s">
         <v>132</v>
@@ -2922,7 +2928,7 @@
         <v>12</v>
       </c>
       <c r="BO3" s="38" t="str">
-        <f t="shared" ref="BO3:BO20" si="13">IF(BM3=0,"NA",BN3-$AA3)</f>
+        <f t="shared" ref="BO3:BO5" si="13">IF(BM3=0,"NA",BN3-$AA3)</f>
         <v>NA</v>
       </c>
       <c r="BP3" s="36">
@@ -2932,7 +2938,7 @@
         <v>1.2581018518518519E-2</v>
       </c>
       <c r="BR3" s="38">
-        <f t="shared" ref="BR3:BR20" si="14">IF(BP3=0,"NA",BQ3-$AA3)</f>
+        <f t="shared" ref="BR3:BR5" si="14">IF(BP3=0,"NA",BQ3-$AA3)</f>
         <v>5.1504629629629643E-3</v>
       </c>
       <c r="BS3" s="36">
@@ -2952,7 +2958,7 @@
         <v>2.4328703703703703E-2</v>
       </c>
       <c r="BX3" s="38">
-        <f t="shared" ref="BX3:BX20" si="16">IF(BV3=0,"NA",BW3-$AA3)</f>
+        <f t="shared" ref="BX3:BX5" si="16">IF(BV3=0,"NA",BW3-$AA3)</f>
         <v>1.6898148148148148E-2</v>
       </c>
       <c r="BY3" s="36"/>
@@ -3906,7 +3912,7 @@
         <v>12</v>
       </c>
       <c r="BO7" s="38" t="str">
-        <f t="shared" ref="BO7:BO24" si="18">IF(BM7=0,"NA",BN7-$AA7)</f>
+        <f t="shared" ref="BO7:BO20" si="18">IF(BM7=0,"NA",BN7-$AA7)</f>
         <v>NA</v>
       </c>
       <c r="BP7" s="36">
@@ -3916,7 +3922,7 @@
         <v>1.1666666666666667E-2</v>
       </c>
       <c r="BR7" s="38">
-        <f t="shared" ref="BR7:BR24" si="19">IF(BP7=0,"NA",BQ7-$AA7)</f>
+        <f t="shared" ref="BR7:BR20" si="19">IF(BP7=0,"NA",BQ7-$AA7)</f>
         <v>4.7222222222222231E-3</v>
       </c>
       <c r="BS7" s="36">
@@ -3932,7 +3938,7 @@
       <c r="BV7" s="36"/>
       <c r="BW7" s="39"/>
       <c r="BX7" s="38" t="str">
-        <f t="shared" ref="BX7:BX24" si="20">IF(BV7=0,"NA",BW7-$AA7)</f>
+        <f t="shared" ref="BX7:BX20" si="20">IF(BV7=0,"NA",BW7-$AA7)</f>
         <v>NA</v>
       </c>
       <c r="BY7" s="36"/>
@@ -6235,11 +6241,11 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="39">
-        <v>0.48749999999999999</v>
+        <v>8.1250000000000003E-3</v>
       </c>
       <c r="AK17" s="38">
         <f t="shared" si="3"/>
-        <v>0.48402777777777778</v>
+        <v>4.6527777777777782E-3</v>
       </c>
       <c r="AL17" s="36">
         <v>0</v>
